--- a/static/templates/assets_template.xlsx
+++ b/static/templates/assets_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\grc_backend\static\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cydea\grc_backend\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083046E1-8FC9-40B6-931A-284527C94907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB782F74-50B6-482B-8563-C6C224673734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17C1CE52-05C9-4D28-8FBB-D81BA6FCE39E}"/>
   </bookViews>
@@ -607,9 +607,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -669,9 +670,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -709,7 +710,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -815,7 +816,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -957,7 +958,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -978,7 +979,7 @@
     <col min="10" max="10" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1019,7 +1020,7 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1060,7 +1061,7 @@
       <c r="L2">
         <v>1</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="2" t="s">
         <v>31</v>
       </c>
     </row>
